--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.30291</v>
+        <v>17.13504</v>
       </c>
       <c r="D2" t="n">
-        <v>17.18177</v>
+        <v>16.98642</v>
       </c>
       <c r="E2" t="n">
-        <v>16.76275</v>
+        <v>17.05909</v>
       </c>
       <c r="F2" t="n">
-        <v>44.4544</v>
+        <v>44.15709</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05132</v>
+        <v>0.05181</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89131</v>
+        <v>1.85568</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.35145</v>
+        <v>17.41804</v>
       </c>
       <c r="D3" t="n">
-        <v>17.48921</v>
+        <v>17.06025</v>
       </c>
       <c r="E3" t="n">
-        <v>17.37712</v>
+        <v>17.09515</v>
       </c>
       <c r="F3" t="n">
-        <v>42.60242</v>
+        <v>43.55418</v>
       </c>
       <c r="G3" t="n">
-        <v>0.053</v>
+        <v>0.05103</v>
       </c>
       <c r="H3" t="n">
-        <v>1.92097</v>
+        <v>1.87281</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.26774</v>
+        <v>17.38051</v>
       </c>
       <c r="D4" t="n">
-        <v>16.82305</v>
+        <v>17.12964</v>
       </c>
       <c r="E4" t="n">
-        <v>17.38378</v>
+        <v>17.23398</v>
       </c>
       <c r="F4" t="n">
-        <v>43.27562</v>
+        <v>44.64235</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05267</v>
+        <v>0.05303</v>
       </c>
       <c r="H4" t="n">
-        <v>1.89867</v>
+        <v>1.84705</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.38946</v>
+        <v>17.12446</v>
       </c>
       <c r="D6" t="n">
-        <v>16.44573</v>
+        <v>16.85564</v>
       </c>
       <c r="E6" t="n">
-        <v>17.01744</v>
+        <v>16.91957</v>
       </c>
       <c r="F6" t="n">
-        <v>22.39283</v>
+        <v>22.58212</v>
       </c>
       <c r="G6" t="n">
-        <v>35.84913</v>
+        <v>35.48626</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.1113</v>
+        <v>17.0987</v>
       </c>
       <c r="D7" t="n">
-        <v>16.48935</v>
+        <v>16.0533</v>
       </c>
       <c r="E7" t="n">
-        <v>16.91231</v>
+        <v>17.00858</v>
       </c>
       <c r="F7" t="n">
-        <v>22.64535</v>
+        <v>21.94429</v>
       </c>
       <c r="G7" t="n">
-        <v>35.87465</v>
+        <v>35.52407</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.41886</v>
+        <v>16.84244</v>
       </c>
       <c r="D8" t="n">
-        <v>16.20781</v>
+        <v>16.45956</v>
       </c>
       <c r="E8" t="n">
-        <v>17.4719</v>
+        <v>16.79594</v>
       </c>
       <c r="F8" t="n">
-        <v>22.45482</v>
+        <v>22.24872</v>
       </c>
       <c r="G8" t="n">
-        <v>35.95385</v>
+        <v>34.92676</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6250599999999999</v>
+        <v>0.62241</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1442</v>
+        <v>1.14427</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61129</v>
+        <v>0.63166</v>
       </c>
       <c r="D11" t="n">
-        <v>1.13862</v>
+        <v>1.15165</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6318</v>
+        <v>0.62326</v>
       </c>
       <c r="D12" t="n">
-        <v>1.15918</v>
+        <v>1.14462</v>
       </c>
     </row>
   </sheetData>
